--- a/ig/main/ValueSet-jdv-j368-categorie-etablissement-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-j368-categorie-etablissement-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250422120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T18:02:28.249+00:00</t>
+    <t>2026-05-05T12:00:00.249+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>JDV à l'image de l'ensemble des valeurs actives de la terminologie TRE_R66-CategorieEtablissement</t>
+    <t>JDV pour le CISIS reprenant l'ensemble des valeurs actives et obsolètes de niveau 4 dans la TreR397CategorieEntiteGeographiqueExercice</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,13 +99,10 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>=</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
@@ -114,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
   </si>
 </sst>
 </file>
@@ -378,7 +375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -387,40 +384,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
         <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>13</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
